--- a/input/reg_health_wellbeing.xlsx
+++ b/input/reg_health_wellbeing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\andy_local\SimPaths project files\SimPaths\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B698CB95-923A-4345-BDDC-5EBAC21A34E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FCDA3BB-82AC-46EB-9E90-8440F73C9A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28665" yWindow="-135" windowWidth="29070" windowHeight="15750" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="10" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="46">
   <si>
     <t>REGRESSOR</t>
   </si>
@@ -164,6 +164,9 @@
   </si>
   <si>
     <t>Covid_2021_D</t>
+  </si>
+  <si>
+    <t>D_Econ_benefits_UC</t>
   </si>
 </sst>
 </file>
@@ -556,13 +559,13 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11572986-38C7-4EDA-A20B-58ABE51A5256}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -602,8 +605,11 @@
       <c r="M1" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
@@ -643,8 +649,11 @@
       <c r="M2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
@@ -684,8 +693,11 @@
       <c r="M3" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
@@ -725,8 +737,11 @@
       <c r="M4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
@@ -766,8 +781,11 @@
       <c r="M5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>37</v>
       </c>
@@ -807,8 +825,11 @@
       <c r="M6" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
@@ -848,8 +869,11 @@
       <c r="M7" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>39</v>
       </c>
@@ -889,8 +913,11 @@
       <c r="M8" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>40</v>
       </c>
@@ -930,8 +957,11 @@
       <c r="M9" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>41</v>
       </c>
@@ -971,8 +1001,11 @@
       <c r="M10" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>43</v>
       </c>
@@ -1012,8 +1045,11 @@
       <c r="M11" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
@@ -1052,6 +1088,53 @@
       </c>
       <c r="M12" s="2">
         <v>9.5756574069857958E-4</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="2">
+        <v>-0.41599999999999998</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2">
+        <v>1.3455999999999999E-2</v>
       </c>
     </row>
   </sheetData>
@@ -4306,13 +4389,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{815F9260-CCEF-41E5-95CB-A3793F4D911F}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4352,8 +4435,11 @@
       <c r="M1" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
@@ -4393,8 +4479,11 @@
       <c r="M2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
@@ -4434,8 +4523,11 @@
       <c r="M3" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
@@ -4475,8 +4567,11 @@
       <c r="M4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
@@ -4516,8 +4611,11 @@
       <c r="M5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>37</v>
       </c>
@@ -4557,8 +4655,11 @@
       <c r="M6" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
@@ -4598,8 +4699,11 @@
       <c r="M7" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>39</v>
       </c>
@@ -4639,8 +4743,11 @@
       <c r="M8" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>40</v>
       </c>
@@ -4680,8 +4787,11 @@
       <c r="M9" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>41</v>
       </c>
@@ -4721,8 +4831,11 @@
       <c r="M10" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>43</v>
       </c>
@@ -4762,8 +4875,11 @@
       <c r="M11" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
@@ -4802,6 +4918,53 @@
       </c>
       <c r="M12" s="2">
         <v>1.779505443658538E-2</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="2">
+        <v>-0.69799999999999995</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2">
+        <v>7.7284000000000005E-2</v>
       </c>
     </row>
   </sheetData>
@@ -4811,13 +4974,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E52CA595-EF5A-4B89-ADDA-26B507FA5B54}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4857,8 +5020,11 @@
       <c r="M1" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
@@ -4898,8 +5064,11 @@
       <c r="M2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
@@ -4939,8 +5108,11 @@
       <c r="M3" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
@@ -4980,8 +5152,11 @@
       <c r="M4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
@@ -5021,8 +5196,11 @@
       <c r="M5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>37</v>
       </c>
@@ -5062,8 +5240,11 @@
       <c r="M6" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
@@ -5103,8 +5284,11 @@
       <c r="M7" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>39</v>
       </c>
@@ -5144,8 +5328,11 @@
       <c r="M8" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>40</v>
       </c>
@@ -5185,8 +5372,11 @@
       <c r="M9" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>41</v>
       </c>
@@ -5226,8 +5416,11 @@
       <c r="M10" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>43</v>
       </c>
@@ -5267,8 +5460,11 @@
       <c r="M11" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
@@ -5307,6 +5503,53 @@
       </c>
       <c r="M12" s="2">
         <v>1.8359183623123131E-2</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="2">
+        <v>-0.69799999999999995</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2">
+        <v>7.7284000000000005E-2</v>
       </c>
     </row>
   </sheetData>
@@ -8561,13 +8804,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9FA8D6C-9D41-4B83-96DC-3CE185883661}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8607,8 +8850,11 @@
       <c r="M1" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
@@ -8648,8 +8894,11 @@
       <c r="M2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
@@ -8689,8 +8938,11 @@
       <c r="M3" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
@@ -8730,8 +8982,11 @@
       <c r="M4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
@@ -8771,8 +9026,11 @@
       <c r="M5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>37</v>
       </c>
@@ -8812,8 +9070,11 @@
       <c r="M6" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
@@ -8853,8 +9114,11 @@
       <c r="M7" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>39</v>
       </c>
@@ -8894,8 +9158,11 @@
       <c r="M8" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>40</v>
       </c>
@@ -8935,8 +9202,11 @@
       <c r="M9" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>41</v>
       </c>
@@ -8976,8 +9246,11 @@
       <c r="M10" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>43</v>
       </c>
@@ -9017,8 +9290,11 @@
       <c r="M11" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
@@ -9057,6 +9333,53 @@
       </c>
       <c r="M12" s="2">
         <v>1.0046029873614293E-2</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="2">
+        <v>-0.23599999999999999</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2">
+        <v>4.5796000000000003E-2</v>
       </c>
     </row>
   </sheetData>
@@ -9066,13 +9389,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90A3630-8F41-4CB5-B1DE-F906AA02BA4D}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9112,8 +9435,11 @@
       <c r="M1" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
@@ -9153,8 +9479,11 @@
       <c r="M2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
@@ -9194,8 +9523,11 @@
       <c r="M3" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
@@ -9235,8 +9567,11 @@
       <c r="M4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
@@ -9276,8 +9611,11 @@
       <c r="M5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>37</v>
       </c>
@@ -9317,8 +9655,11 @@
       <c r="M6" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
@@ -9358,8 +9699,11 @@
       <c r="M7" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>39</v>
       </c>
@@ -9399,8 +9743,11 @@
       <c r="M8" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>40</v>
       </c>
@@ -9440,8 +9787,11 @@
       <c r="M9" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>41</v>
       </c>
@@ -9481,8 +9831,11 @@
       <c r="M10" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>43</v>
       </c>
@@ -9522,8 +9875,11 @@
       <c r="M11" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
@@ -9562,6 +9918,53 @@
       </c>
       <c r="M12" s="2">
         <v>1.1107883785965942E-2</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="2">
+        <v>-0.23599999999999999</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2">
+        <v>4.5796000000000003E-2</v>
       </c>
     </row>
   </sheetData>
@@ -12816,13 +13219,13 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8271DA1-113B-44D0-8CF2-767CF072D053}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12862,8 +13265,11 @@
       <c r="M1" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
@@ -12903,8 +13309,11 @@
       <c r="M2" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
@@ -12944,8 +13353,11 @@
       <c r="M3" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
@@ -12985,8 +13397,11 @@
       <c r="M4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
@@ -13026,8 +13441,11 @@
       <c r="M5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>37</v>
       </c>
@@ -13067,8 +13485,11 @@
       <c r="M6" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
@@ -13108,8 +13529,11 @@
       <c r="M7" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>39</v>
       </c>
@@ -13149,8 +13573,11 @@
       <c r="M8" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>40</v>
       </c>
@@ -13190,8 +13617,11 @@
       <c r="M9" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>41</v>
       </c>
@@ -13231,8 +13661,11 @@
       <c r="M10" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>43</v>
       </c>
@@ -13272,8 +13705,11 @@
       <c r="M11" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
@@ -13312,6 +13748,53 @@
       </c>
       <c r="M12" s="2">
         <v>9.2539235417522174E-4</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="2">
+        <v>-0.41599999999999998</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2">
+        <v>1.3455999999999999E-2</v>
       </c>
     </row>
   </sheetData>
